--- a/src/test/resources/testdata/data.xlsx
+++ b/src/test/resources/testdata/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SeleniumTraining\seleniumworkspace\com.orangehrm.automate\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A21D7A7-6394-47E3-82D9-6911D196F9C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3558E000-E865-4789-820A-BA93053194DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="8">
   <si>
     <t>Admin</t>
   </si>
@@ -34,31 +34,22 @@
     <t>admin123</t>
   </si>
   <si>
-    <t>user_01</t>
-  </si>
-  <si>
-    <t>user_02</t>
-  </si>
-  <si>
     <t>Emily Jones</t>
   </si>
   <si>
-    <t>james123456</t>
-  </si>
-  <si>
     <t>ESS</t>
   </si>
   <si>
-    <t>Linda Anderson</t>
-  </si>
-  <si>
-    <t>linda1234567</t>
-  </si>
-  <si>
     <t>Ranga Akunuri</t>
   </si>
   <si>
-    <t>ranga1234567</t>
+    <t>linda12345678</t>
+  </si>
+  <si>
+    <t>ranga12345678</t>
+  </si>
+  <si>
+    <t>james1234568</t>
   </si>
 </sst>
 </file>
@@ -376,7 +367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -389,22 +380,6 @@
       </c>
       <c r="B1" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -429,33 +404,33 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -463,16 +438,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testdata/data.xlsx
+++ b/src/test/resources/testdata/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SeleniumTraining\seleniumworkspace\com.orangehrm.automate\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3558E000-E865-4789-820A-BA93053194DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE3B53F-0214-4FAA-A414-72890DC7FFAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t>Admin</t>
   </si>
@@ -34,22 +34,19 @@
     <t>admin123</t>
   </si>
   <si>
-    <t>Emily Jones</t>
-  </si>
-  <si>
     <t>ESS</t>
   </si>
   <si>
-    <t>Ranga Akunuri</t>
-  </si>
-  <si>
-    <t>linda12345678</t>
-  </si>
-  <si>
-    <t>ranga12345678</t>
-  </si>
-  <si>
-    <t>james1234568</t>
+    <t>Amelia  Brown</t>
+  </si>
+  <si>
+    <t>amelia12345678</t>
+  </si>
+  <si>
+    <t>Ravi M B</t>
+  </si>
+  <si>
+    <t>ravi87654321</t>
   </si>
 </sst>
 </file>
@@ -389,7 +386,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29A8F0CC-7699-4E96-8D29-BE61F4AB24C0}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
@@ -404,49 +401,32 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
         <v>6</v>
       </c>
     </row>

--- a/src/test/resources/testdata/data.xlsx
+++ b/src/test/resources/testdata/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SeleniumTraining\seleniumworkspace\com.orangehrm.automate\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE3B53F-0214-4FAA-A414-72890DC7FFAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5262D2F2-40A7-43CD-B8AF-3A38EA6282D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
   <si>
     <t>Admin</t>
   </si>
@@ -37,16 +37,13 @@
     <t>ESS</t>
   </si>
   <si>
-    <t>Amelia  Brown</t>
-  </si>
-  <si>
-    <t>amelia12345678</t>
-  </si>
-  <si>
-    <t>Ravi M B</t>
-  </si>
-  <si>
-    <t>ravi87654321</t>
+    <t>James Butler</t>
+  </si>
+  <si>
+    <t>james12345678</t>
+  </si>
+  <si>
+    <t>james87654321</t>
   </si>
 </sst>
 </file>
@@ -418,16 +415,16 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testdata/data.xlsx
+++ b/src/test/resources/testdata/data.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SeleniumTraining\seleniumworkspace\com.orangehrm.automate\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5262D2F2-40A7-43CD-B8AF-3A38EA6282D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACA7686-450A-41BE-A413-E7AA724DFF1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="8">
   <si>
     <t>Admin</t>
   </si>
@@ -37,6 +38,9 @@
     <t>ESS</t>
   </si>
   <si>
+    <t>ravi87654321</t>
+  </si>
+  <si>
     <t>James Butler</t>
   </si>
   <si>
@@ -44,19 +48,28 @@
   </si>
   <si>
     <t>james87654321</t>
+  </si>
+  <si>
+    <t>ravi12345678</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF38455D"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -79,8 +92,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,16 +412,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -415,16 +429,39 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DDA767A-7CC1-478B-BECC-892633003BDA}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
